--- a/sem/KAJ - hodnocení semestrální práce.xlsx
+++ b/sem/KAJ - hodnocení semestrální práce.xlsx
@@ -8,26 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\KAJ\sem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12316D69-C544-4DC4-9E3E-BE02BB1C3A2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66DD7C8E-36E3-47BE-8F2D-994666F45DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -36,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="49">
   <si>
     <t>Kategorie</t>
   </si>
@@ -180,13 +169,10 @@
     <t>My</t>
   </si>
   <si>
-    <t>add fírst-child</t>
-  </si>
-  <si>
-    <t>localstorage</t>
-  </si>
-  <si>
-    <t>todo</t>
+    <t>TODO last</t>
+  </si>
+  <si>
+    <t>maybe</t>
   </si>
 </sst>
 </file>
@@ -494,9 +480,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motiv Office 2013–2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motiv Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 –⁠ 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -534,7 +520,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 –⁠ 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -640,7 +626,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 –⁠ 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -782,7 +768,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1004,6 +990,9 @@
         <v>1</v>
       </c>
       <c r="G4" s="6"/>
+      <c r="H4" t="s">
+        <v>47</v>
+      </c>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
@@ -1074,7 +1063,7 @@
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="15" t="s">
         <v>6</v>
@@ -1084,6 +1073,9 @@
       </c>
       <c r="G6" s="16" t="s">
         <v>10</v>
+      </c>
+      <c r="H6" t="s">
+        <v>47</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
@@ -1272,6 +1264,9 @@
         <v>1</v>
       </c>
       <c r="G9" s="6"/>
+      <c r="H9" t="s">
+        <v>48</v>
+      </c>
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
@@ -1328,7 +1323,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="10">
@@ -1505,7 +1500,7 @@
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>6</v>
@@ -1514,9 +1509,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="6"/>
-      <c r="H13" s="26" t="s">
-        <v>47</v>
-      </c>
+      <c r="H13" s="26"/>
       <c r="AK13" s="7"/>
     </row>
     <row r="14" spans="1:54" x14ac:dyDescent="0.2">
@@ -1526,7 +1519,7 @@
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
       <c r="D14" s="22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="10">
@@ -1613,6 +1606,9 @@
         <v>2</v>
       </c>
       <c r="G16" s="6"/>
+      <c r="H16" t="s">
+        <v>48</v>
+      </c>
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
@@ -1881,7 +1877,7 @@
       </c>
       <c r="C22" s="6"/>
       <c r="D22" s="22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E22" s="17" t="s">
         <v>6</v>
@@ -1890,9 +1886,7 @@
         <v>3</v>
       </c>
       <c r="G22" s="6"/>
-      <c r="H22" s="26" t="s">
-        <v>48</v>
-      </c>
+      <c r="H22" s="26"/>
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -1948,16 +1942,14 @@
       </c>
       <c r="C23" s="6"/>
       <c r="D23" s="22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E23" s="6"/>
       <c r="F23" s="10">
         <v>2</v>
       </c>
       <c r="G23" s="6"/>
-      <c r="H23" s="26" t="s">
-        <v>49</v>
-      </c>
+      <c r="H23" s="26"/>
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
@@ -2021,6 +2013,9 @@
         <v>1</v>
       </c>
       <c r="G24" s="6"/>
+      <c r="H24" t="s">
+        <v>48</v>
+      </c>
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
@@ -2140,7 +2135,7 @@
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" s="6"/>
       <c r="F26" s="10">
@@ -2388,13 +2383,13 @@
       <c r="F34" s="9"/>
       <c r="G34" s="6"/>
     </row>
-    <row r="35" spans="1:7" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
       <c r="D35" s="23">
         <f>SUM(D2:D33)</f>
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E35" s="19" t="s">
         <v>45</v>
@@ -2595,36 +2590,36 @@
       <c r="E96" s="21"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="G4">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="greaterThanOrEqual">
+      <formula>F4:F28</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="lessThan">
+      <formula>F4:F28</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G5:G28">
-    <cfRule type="cellIs" dxfId="7" priority="3" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="greaterThanOrEqual">
       <formula>F5:F30</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="lessThan">
       <formula>F5:F30</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I4:K4">
+    <cfRule type="cellIs" dxfId="3" priority="9" operator="greaterThanOrEqual">
+      <formula>I4:I28</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="10" operator="lessThan">
+      <formula>I4:I28</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I5:K28">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThanOrEqual">
       <formula>I5:I30</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>I5:I30</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G4">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="greaterThanOrEqual">
-      <formula>F4:F28</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="6" operator="lessThan">
-      <formula>F4:F28</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I4:K4">
-    <cfRule type="cellIs" dxfId="1" priority="9" operator="greaterThanOrEqual">
-      <formula>I4:I28</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="10" operator="lessThan">
-      <formula>I4:I28</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
